--- a/main/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/main/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T08:08:15+00:00</t>
+    <t>2026-05-18T14:11:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/main/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:11:29+00:00</t>
+    <t>2026-05-21T09:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/main/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T09:18:21+00:00</t>
+    <t>2026-06-01T14:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/main/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:41:15+00:00</t>
+    <t>2026-06-01T15:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/main/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T15:18:33+00:00</t>
+    <t>2026-06-02T07:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/main/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2235" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2234" uniqueCount="456">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T07:35:19+00:00</t>
+    <t>2026-06-04T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1188,13 +1188,7 @@
     <t>The anatomic structures examined. See DICOM Part 16 Annex L (http://dicom.nema.org/medical/dicom/current/output/chtml/part16/chapter_L.html) for DICOM to SNOMED-CT mappings. The bodySite may indicate the laterality of body part imaged; if so, it shall be consistent with any content of ImagingStudy.series.laterality.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -1796,7 +1790,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="49.63671875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="34.12109375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="61.59375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -6648,13 +6642,11 @@
         <v>78</v>
       </c>
       <c r="X42" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="Y42" s="2"/>
+      <c r="Z42" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>78</v>
@@ -6690,10 +6682,10 @@
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>78</v>
@@ -6704,10 +6696,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6733,10 +6725,10 @@
         <v>176</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6767,7 +6759,7 @@
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>78</v>
@@ -6785,7 +6777,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6803,10 +6795,10 @@
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>78</v>
@@ -6817,10 +6809,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6843,13 +6835,13 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6900,7 +6892,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6918,10 +6910,10 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>78</v>
@@ -6932,10 +6924,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6961,10 +6953,10 @@
         <v>202</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7015,7 +7007,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7036,7 +7028,7 @@
         <v>207</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>78</v>
@@ -7047,14 +7039,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7076,16 +7068,16 @@
         <v>313</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
@@ -7134,7 +7126,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7149,13 +7141,13 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>235</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -7166,10 +7158,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7281,10 +7273,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7398,10 +7390,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7517,10 +7509,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7546,14 +7538,14 @@
         <v>267</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7581,10 +7573,10 @@
         <v>270</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>78</v>
@@ -7602,7 +7594,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7634,10 +7626,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7660,13 +7652,13 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7717,7 +7709,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>89</v>
@@ -7735,24 +7727,24 @@
         <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>414</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7778,10 +7770,10 @@
         <v>313</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7832,7 +7824,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7850,7 +7842,7 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>78</v>
@@ -7864,10 +7856,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7979,10 +7971,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8008,10 +8000,10 @@
         <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8050,7 +8042,7 @@
         <v>78</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AC54" s="2"/>
       <c r="AD54" t="s" s="2">
@@ -8092,13 +8084,13 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>78</v>
@@ -8120,13 +8112,13 @@
         <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8186,7 +8178,7 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>140</v>
@@ -8209,10 +8201,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8328,14 +8320,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8357,16 +8349,16 @@
         <v>91</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -8379,7 +8371,7 @@
         <v>78</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>78</v>
@@ -8415,7 +8407,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>89</v>
@@ -8436,7 +8428,7 @@
         <v>337</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
@@ -8447,14 +8439,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8476,10 +8468,10 @@
         <v>176</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8510,7 +8502,7 @@
       </c>
       <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -8528,7 +8520,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>89</v>
@@ -8546,10 +8538,10 @@
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -8560,14 +8552,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8589,10 +8581,10 @@
         <v>247</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8643,7 +8635,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8661,10 +8653,10 @@
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -8675,10 +8667,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8704,13 +8696,13 @@
         <v>307</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8760,7 +8752,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8778,10 +8770,10 @@
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>

--- a/main/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/main/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T15:31:02+00:00</t>
+    <t>2026-06-16T14:27:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/main/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:27:29+00:00</t>
+    <t>2026-06-18T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -797,7 +797,7 @@
 </t>
   </si>
   <si>
-    <t>Number of Study Related Series</t>
+    <t>Nombre de séries</t>
   </si>
   <si>
     <t>Number of Series in the Study. This value given may be larger than the number of series elements this Resource contains due to resource availability, security, or other factors. This element should be present if any series elements are present.</t>
@@ -4384,7 +4384,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>245</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>89</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>78</v>

--- a/main/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/main/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:40:49+00:00</t>
+    <t>2026-06-22T09:35:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
